--- a/excel/output_stats_sfvv/covariance/PerSubgraphStats.xlsx
+++ b/excel/output_stats_sfvv/covariance/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,10 +823,10 @@
         <v>0.6</v>
       </c>
       <c r="N8" t="n">
-        <v>344.164</v>
+        <v>344.844</v>
       </c>
       <c r="O8" t="n">
-        <v>346</v>
+        <v>346.68</v>
       </c>
     </row>
     <row r="9">
@@ -870,10 +870,10 @@
         <v>0.6</v>
       </c>
       <c r="N9" t="n">
-        <v>344.164</v>
+        <v>344.844</v>
       </c>
       <c r="O9" t="n">
-        <v>353.9</v>
+        <v>354.93</v>
       </c>
     </row>
     <row r="10">
@@ -917,10 +917,10 @@
         <v>0.6</v>
       </c>
       <c r="N10" t="n">
-        <v>352.301</v>
+        <v>353.378</v>
       </c>
       <c r="O10" t="n">
-        <v>354.75</v>
+        <v>355.83</v>
       </c>
     </row>
     <row r="11">
@@ -964,10 +964,10 @@
         <v>0.6</v>
       </c>
       <c r="N11" t="n">
-        <v>352.301</v>
+        <v>353.378</v>
       </c>
       <c r="O11" t="n">
-        <v>354.79</v>
+        <v>355.89</v>
       </c>
     </row>
     <row r="12">
@@ -1011,10 +1011,10 @@
         <v>0.6</v>
       </c>
       <c r="N12" t="n">
-        <v>351.241</v>
+        <v>352.318</v>
       </c>
       <c r="O12" t="n">
-        <v>353.56</v>
+        <v>354.69</v>
       </c>
     </row>
     <row r="13">
@@ -1058,10 +1058,10 @@
         <v>0.6</v>
       </c>
       <c r="N13" t="n">
-        <v>351.24</v>
+        <v>352.318</v>
       </c>
       <c r="O13" t="n">
-        <v>353.55</v>
+        <v>354.68</v>
       </c>
     </row>
     <row r="14">
@@ -1069,34 +1069,34 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>1.14878e-09</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4.33333e-09</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.265104</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4.978060000000001e-18</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>923077000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>3000000000</v>
@@ -1116,34 +1116,34 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00127918</v>
+        <v>1.14878e-09</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00517646</v>
+        <v>4.33333e-09</v>
       </c>
       <c r="E15" t="n">
-        <v>0.247115</v>
+        <v>0.265104</v>
       </c>
       <c r="F15" t="n">
-        <v>6.62163e-06</v>
+        <v>4.978060000000001e-18</v>
       </c>
       <c r="G15" t="n">
-        <v>730344000</v>
+        <v>923077000</v>
       </c>
       <c r="H15" t="n">
-        <v>3780600</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1681200</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>15529400</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>3000000000</v>
@@ -1155,7 +1155,7 @@
         <v>351.22</v>
       </c>
       <c r="O15" t="n">
-        <v>353.23</v>
+        <v>353.24</v>
       </c>
     </row>
     <row r="16">
@@ -1163,34 +1163,34 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>1.80529e-09</v>
+        <v>0.00127918</v>
       </c>
       <c r="D16" t="n">
-        <v>7e-09</v>
+        <v>0.00517646</v>
       </c>
       <c r="E16" t="n">
-        <v>0.257899</v>
+        <v>0.247115</v>
       </c>
       <c r="F16" t="n">
-        <v>1.26371e-17</v>
+        <v>6.62163e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>714286000</v>
+        <v>730344000</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3780600</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1681200</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>15529400</v>
       </c>
       <c r="L16" t="n">
         <v>3000000000</v>
@@ -1199,10 +1199,10 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>350.153</v>
+        <v>351.22</v>
       </c>
       <c r="O16" t="n">
-        <v>350.3</v>
+        <v>353.23</v>
       </c>
     </row>
     <row r="17">
@@ -1210,34 +1210,34 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1.06408e-09</v>
+        <v>1.80529e-09</v>
       </c>
       <c r="D17" t="n">
-        <v>4.33333e-09</v>
+        <v>7e-09</v>
       </c>
       <c r="E17" t="n">
-        <v>0.245557</v>
+        <v>0.257899</v>
       </c>
       <c r="F17" t="n">
-        <v>4.61101e-18</v>
+        <v>1.26371e-17</v>
       </c>
       <c r="G17" t="n">
-        <v>692308000</v>
+        <v>714286000</v>
       </c>
       <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L17" t="n">
         <v>3000000000</v>
@@ -1257,25 +1257,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>2.35661e-10</v>
+        <v>1.06408e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>6.66667e-10</v>
+        <v>4.33333e-09</v>
       </c>
       <c r="E18" t="n">
-        <v>0.353492</v>
+        <v>0.245557</v>
       </c>
       <c r="F18" t="n">
-        <v>1.57108e-19</v>
+        <v>4.61101e-18</v>
       </c>
       <c r="G18" t="n">
-        <v>3000000000</v>
+        <v>692308000</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
         <v>3000000000</v>
@@ -1293,10 +1293,10 @@
         <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>350.152</v>
+        <v>350.153</v>
       </c>
       <c r="O18" t="n">
-        <v>350.29</v>
+        <v>350.3</v>
       </c>
     </row>
     <row r="19">
@@ -1304,34 +1304,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>1.85627e-09</v>
+        <v>2.35661e-10</v>
       </c>
       <c r="D19" t="n">
-        <v>6.66667e-09</v>
+        <v>6.66667e-10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.278441</v>
+        <v>0.353492</v>
       </c>
       <c r="F19" t="n">
-        <v>1.23752e-17</v>
+        <v>1.57108e-19</v>
       </c>
       <c r="G19" t="n">
-        <v>1200000000</v>
+        <v>3000000000</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>3000000000</v>
@@ -1340,10 +1340,10 @@
         <v>0.6</v>
       </c>
       <c r="N19" t="n">
-        <v>350.151</v>
+        <v>350.152</v>
       </c>
       <c r="O19" t="n">
-        <v>350.23</v>
+        <v>350.29</v>
       </c>
     </row>
     <row r="20">
@@ -1351,34 +1351,34 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>4.90752e-10</v>
+        <v>1.85627e-09</v>
       </c>
       <c r="D20" t="n">
-        <v>1.66667e-09</v>
+        <v>6.66667e-09</v>
       </c>
       <c r="E20" t="n">
-        <v>0.294451</v>
+        <v>0.278441</v>
       </c>
       <c r="F20" t="n">
-        <v>8.179190000000001e-19</v>
+        <v>1.23752e-17</v>
       </c>
       <c r="G20" t="n">
-        <v>1800000000</v>
+        <v>1200000000</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L20" t="n">
         <v>3000000000</v>
@@ -1390,7 +1390,7 @@
         <v>350.151</v>
       </c>
       <c r="O20" t="n">
-        <v>350.21</v>
+        <v>350.23</v>
       </c>
     </row>
     <row r="21">
@@ -1398,34 +1398,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>5.06373e-09</v>
+        <v>4.90752e-10</v>
       </c>
       <c r="D21" t="n">
-        <v>2.03333e-08</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E21" t="n">
-        <v>0.249036</v>
+        <v>0.294451</v>
       </c>
       <c r="F21" t="n">
-        <v>1.02963e-16</v>
+        <v>8.179190000000001e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>688525000</v>
+        <v>1800000000</v>
       </c>
       <c r="H21" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>3000000000</v>
@@ -1434,10 +1434,10 @@
         <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O21" t="n">
-        <v>350.17</v>
+        <v>350.21</v>
       </c>
     </row>
     <row r="22">
@@ -1445,34 +1445,34 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>4.76522e-10</v>
+        <v>5.06373e-09</v>
       </c>
       <c r="D22" t="n">
-        <v>2e-09</v>
+        <v>2.03333e-08</v>
       </c>
       <c r="E22" t="n">
-        <v>0.238261</v>
+        <v>0.249036</v>
       </c>
       <c r="F22" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>1.02963e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>500000000</v>
+        <v>688525000</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="L22" t="n">
         <v>3000000000</v>
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
         <v>4.76522e-10</v>
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>6.24265e-10</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D24" t="n">
-        <v>2.33333e-09</v>
+        <v>2e-09</v>
       </c>
       <c r="E24" t="n">
-        <v>0.267542</v>
+        <v>0.238261</v>
       </c>
       <c r="F24" t="n">
-        <v>1.45662e-18</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G24" t="n">
-        <v>857143000</v>
+        <v>500000000</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>3000000000</v>
@@ -1575,7 +1575,7 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O24" t="n">
         <v>350.17</v>
@@ -1586,7 +1586,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
         <v>6.24265e-10</v>
@@ -1633,34 +1633,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>1.48585e-09</v>
+        <v>6.24265e-10</v>
       </c>
       <c r="D26" t="n">
-        <v>5.66667e-09</v>
+        <v>2.33333e-09</v>
       </c>
       <c r="E26" t="n">
-        <v>0.262208</v>
+        <v>0.267542</v>
       </c>
       <c r="F26" t="n">
-        <v>8.419790000000001e-18</v>
+        <v>1.45662e-18</v>
       </c>
       <c r="G26" t="n">
-        <v>705882000</v>
+        <v>857143000</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
         <v>3000000000</v>
@@ -1669,7 +1669,7 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O26" t="n">
         <v>350.17</v>
@@ -1680,45 +1680,92 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.48585e-09</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5.66667e-09</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.262208</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.419790000000001e-18</v>
+      </c>
+      <c r="G27" t="n">
+        <v>705882000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>17</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C27" t="n">
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="n">
         <v>1.21265e-10</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D28" t="n">
         <v>3.33333e-10</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E28" t="n">
         <v>0.363794</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>4.04216e-20</v>
       </c>
-      <c r="G27" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="G28" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="L28" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N28" t="n">
         <v>350.151</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O28" t="n">
         <v>350.22</v>
       </c>
     </row>
